--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46232.624382141206</v>
+        <v>46279.14474496528</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>233</v>
@@ -5716,8 +5716,8 @@
       <c r="R73" s="9">
         <v>46286</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>32</v>
+      <c r="S73" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46232.62438238426</v>
+        <v>46280.126993576385</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>245</v>
@@ -5983,8 +5983,8 @@
       <c r="R78" s="5">
         <v>46287</v>
       </c>
-      <c r="S78" s="7" t="s">
-        <v>32</v>
+      <c r="S78" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46274.146724861115</v>
+        <v>46281.16859141203</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>221</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46225.870632060185</v>
+        <v>46281.16859314815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>149</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.87064059028</v>
+        <v>46281.168589189816</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>149</v>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46225.87065297454</v>
+        <v>46281.16859033565</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>149</v>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.87067319444</v>
+        <v>46281.16858778935</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>149</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46240.82253846065</v>
+        <v>46281.136327280095</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>256</v>
@@ -6258,8 +6258,8 @@
       <c r="R83" s="9">
         <v>46288</v>
       </c>
-      <c r="S83" s="7" t="s">
-        <v>32</v>
+      <c r="S83" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -432,6 +432,9 @@
     <t xml:space="preserve">Armado  OT 4381 ,Control de calidad   OT 4381  ,Generacion Oc OT 4376 OT 4381  </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216804002821581</t>
   </si>
   <si>
@@ -748,9 +751,6 @@
   </si>
   <si>
     <t xml:space="preserve">Montaje:,Montaje Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216803961867347</t>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46225.866204108796</v>
+        <v>46282.12766203703</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>113</v>
@@ -3342,8 +3342,8 @@
       <c r="R31" s="9">
         <v>46247</v>
       </c>
-      <c r="S31" s="7" t="s">
-        <v>32</v>
+      <c r="S31" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3364,7 +3364,7 @@
         <v>46255.62865344908</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3394,10 +3394,10 @@
         <v>113</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3417,7 +3417,7 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3447,10 +3447,10 @@
         <v>113</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3470,16 +3470,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3500,7 +3500,7 @@
         <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>113</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
@@ -3523,7 +3523,7 @@
         <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3547,7 +3547,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3572,16 +3572,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3599,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3625,7 +3625,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
@@ -3637,16 +3637,16 @@
         <v>46242.20040111111</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46225.86183666666</v>
@@ -3708,10 +3708,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3729,13 +3729,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46225.86185291667</v>
@@ -3765,16 +3765,16 @@
         <v>46225.869796087965</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3792,13 +3792,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46225.86186070602</v>
@@ -3828,16 +3828,16 @@
         <v>46225.870297002315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3853,13 +3853,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46225.861866770836</v>
@@ -3879,16 +3879,16 @@
         <v>46225.870431400464</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3904,13 +3904,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46225.861897951385</v>
@@ -3930,16 +3930,16 @@
         <v>46225.87044054398</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3955,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46225.86190395833</v>
@@ -3981,16 +3981,16 @@
         <v>46225.87046690972</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4006,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46225.86196252315</v>
@@ -4032,7 +4032,7 @@
         <v>46261.50970834491</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>25</v>
@@ -4056,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46225.86196658565</v>
@@ -4079,16 +4079,16 @@
         <v>46261.199512974534</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4104,13 +4104,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>94</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46225.86197478009</v>
@@ -4140,16 +4140,16 @@
         <v>46261.19951315972</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46260</v>
@@ -4167,13 +4167,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="5">
         <v>46260</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="9">
         <v>46225.86198239583</v>
@@ -4203,16 +4203,16 @@
         <v>46261.199514293985</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" s="9">
         <v>46260</v>
@@ -4230,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46225.86198986111</v>
@@ -4266,16 +4266,16 @@
         <v>46262.18550431713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4293,13 +4293,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="9">
         <v>46225.86199775463</v>
@@ -4331,16 +4331,16 @@
         <v>46262.18550420139</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4358,13 +4358,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49" s="9">
         <v>46261</v>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46225.86200543982</v>
@@ -4394,16 +4394,16 @@
         <v>46262.18550445602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4421,13 +4421,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46225.86201293982</v>
@@ -4457,7 +4457,7 @@
         <v>46225.862125590276</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>25</v>
@@ -4481,7 +4481,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46225.86201641204</v>
@@ -4510,10 +4510,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46262</v>
@@ -4531,13 +4531,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46266</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="9">
         <v>46225.86202538194</v>
@@ -4567,16 +4567,16 @@
         <v>46274.141876608795</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4594,13 +4594,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53" s="9">
         <v>46273</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46225.86203225695</v>
@@ -4630,16 +4630,16 @@
         <v>46273.168695127315</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4657,13 +4657,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="9">
         <v>46225.86204296297</v>
@@ -4683,16 +4683,16 @@
         <v>46273.16869601852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4710,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46225.862053379635</v>
@@ -4736,16 +4736,16 @@
         <v>46273.16869688657</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4763,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B57" s="9">
         <v>46225.86206356481</v>
@@ -4789,16 +4789,16 @@
         <v>46273.168692708336</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4816,13 +4816,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46225.86208298611</v>
@@ -4842,16 +4842,16 @@
         <v>46275.146271840276</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4869,13 +4869,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q58" s="5">
         <v>46274</v>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46225.862089999995</v>
@@ -4905,16 +4905,16 @@
         <v>46274.16866800926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4932,13 +4932,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46225.86209783565</v>
@@ -4958,16 +4958,16 @@
         <v>46274.168665474535</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -4985,13 +4985,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46225.86210570602</v>
@@ -5011,16 +5011,16 @@
         <v>46274.168669108796</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" s="5">
         <v>46225.86216362269</v>
@@ -5064,16 +5064,16 @@
         <v>46274.16866429398</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5091,13 +5091,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46225.86219280092</v>
@@ -5117,7 +5117,7 @@
         <v>46225.86232971065</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5141,7 +5141,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46225.86219668981</v>
@@ -5164,16 +5164,16 @@
         <v>46232.19127755787</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I64" s="5">
         <v>46230</v>
@@ -5191,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46231</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46225.86220582176</v>
@@ -5227,16 +5227,16 @@
         <v>46232.19127729167</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I65" s="9">
         <v>46230</v>
@@ -5254,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="9">
         <v>46231</v>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46225.86221482639</v>
@@ -5290,16 +5290,16 @@
         <v>46232.19127710648</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5317,13 +5317,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5343,7 +5343,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
         <v>46225.862222800926</v>
@@ -5353,7 +5353,7 @@
         <v>46232.60338638889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5377,7 +5377,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5390,17 +5390,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46225.862226516205</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46281.16859141203</v>
+        <v>46282.16301920138</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5427,13 +5427,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68" s="5">
         <v>46281</v>
@@ -5441,8 +5441,8 @@
       <c r="R68" s="5">
         <v>46275</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>223</v>
+      <c r="S68" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>46281.16859314815</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5490,10 +5490,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>225</v>
@@ -5516,7 +5516,7 @@
         <v>46281.168589189816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5543,10 +5543,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>227</v>
@@ -5569,7 +5569,7 @@
         <v>46281.16859033565</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5596,10 +5596,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>229</v>
@@ -5622,7 +5622,7 @@
         <v>46281.16858778935</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5649,10 +5649,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>231</v>
@@ -5702,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>234</v>
@@ -5717,7 +5717,7 @@
         <v>46286</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         <v>46238.48726658565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5789,7 +5789,7 @@
         <v>46238.487257326386</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5840,7 +5840,7 @@
         <v>46238.48726778935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5891,7 +5891,7 @@
         <v>46225.870728344904</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5919,7 +5919,7 @@
         <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>241</v>
@@ -5969,7 +5969,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>246</v>
@@ -5984,7 +5984,7 @@
         <v>46287</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6005,7 +6005,7 @@
         <v>46225.870759178244</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6058,7 +6058,7 @@
         <v>46225.870777442135</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6111,7 +6111,7 @@
         <v>46225.870787824075</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6164,7 +6164,7 @@
         <v>46225.87080640046</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6194,7 +6194,7 @@
         <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>252</v>
@@ -6244,13 +6244,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>257</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q83" s="9">
         <v>46288</v>
@@ -6259,7 +6259,7 @@
         <v>46288</v>
       </c>
       <c r="S83" s="12" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
@@ -6280,7 +6280,7 @@
         <v>46238.48726703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6333,7 +6333,7 @@
         <v>46238.48725680556</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6386,7 +6386,7 @@
         <v>46225.870855393514</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6439,7 +6439,7 @@
         <v>46225.87086599537</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6469,7 +6469,7 @@
         <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>265</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46240.8225384375</v>
+        <v>46282.12766146991</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>267</v>
@@ -6519,10 +6519,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>268</v>
@@ -6533,8 +6533,8 @@
       <c r="R88" s="5">
         <v>46289</v>
       </c>
-      <c r="S88" s="7" t="s">
-        <v>32</v>
+      <c r="S88" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6555,7 +6555,7 @@
         <v>46225.87089600695</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6608,7 +6608,7 @@
         <v>46225.87090469907</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6661,7 +6661,7 @@
         <v>46225.870913969906</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6714,7 +6714,7 @@
         <v>46225.870925243056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6744,7 +6744,7 @@
         <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>275</v>
@@ -6794,7 +6794,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>277</v>
@@ -6830,7 +6830,7 @@
         <v>46225.87095484954</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6860,7 +6860,7 @@
         <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>279</v>
@@ -6883,7 +6883,7 @@
         <v>46225.87096165509</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6913,7 +6913,7 @@
         <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>281</v>
@@ -6936,7 +6936,7 @@
         <v>46225.87097416667</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6966,7 +6966,7 @@
         <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>281</v>
@@ -6989,7 +6989,7 @@
         <v>46225.870994074074</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7019,7 +7019,7 @@
         <v>268</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>279</v>
@@ -7119,7 +7119,7 @@
         <v>285</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>291</v>
@@ -7152,7 +7152,7 @@
         <v>46225.87103081019</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7182,7 +7182,7 @@
         <v>288</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>293</v>
@@ -7205,7 +7205,7 @@
         <v>46225.87104060185</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7235,7 +7235,7 @@
         <v>288</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>293</v>
@@ -7258,7 +7258,7 @@
         <v>46225.87104780093</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7288,7 +7288,7 @@
         <v>288</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>296</v>
@@ -7311,7 +7311,7 @@
         <v>46225.871064861116</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7341,7 +7341,7 @@
         <v>288</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>293</v>
@@ -7427,7 +7427,7 @@
         <v>46225.87109706018</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7457,7 +7457,7 @@
         <v>299</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>302</v>
@@ -7480,7 +7480,7 @@
         <v>46225.871105266204</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7510,7 +7510,7 @@
         <v>299</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>302</v>
@@ -7533,7 +7533,7 @@
         <v>46225.87111719907</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7563,7 +7563,7 @@
         <v>299</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>302</v>
@@ -7586,7 +7586,7 @@
         <v>46225.8711331713</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7616,7 +7616,7 @@
         <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>302</v>
@@ -7645,10 +7645,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I109" s="9">
         <v>46296</v>
@@ -7669,7 +7669,7 @@
         <v>285</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>285</v>
@@ -7702,16 +7702,16 @@
         <v>46225.87116359954</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I110" s="5">
         <v>46296</v>
@@ -7732,7 +7732,7 @@
         <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>309</v>
@@ -7755,16 +7755,16 @@
         <v>46225.87117237269</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I111" s="9">
         <v>46296</v>
@@ -7785,7 +7785,7 @@
         <v>307</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>311</v>
@@ -7808,16 +7808,16 @@
         <v>46225.8711906713</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I112" s="5">
         <v>46296</v>
@@ -7838,7 +7838,7 @@
         <v>307</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>311</v>
@@ -7861,16 +7861,16 @@
         <v>46225.87120541667</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I113" s="9">
         <v>46296</v>
@@ -7891,7 +7891,7 @@
         <v>307</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>311</v>
@@ -7920,10 +7920,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I114" s="5">
         <v>46297</v>
@@ -7944,7 +7944,7 @@
         <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>316</v>
@@ -7977,16 +7977,16 @@
         <v>46225.87123498843</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I115" s="9">
         <v>46297</v>
@@ -8007,7 +8007,7 @@
         <v>315</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>318</v>
@@ -8030,16 +8030,16 @@
         <v>46225.87124284722</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I116" s="5">
         <v>46297</v>
@@ -8060,7 +8060,7 @@
         <v>315</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>320</v>
@@ -8083,16 +8083,16 @@
         <v>46225.87125150463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I117" s="9">
         <v>46297</v>
@@ -8113,7 +8113,7 @@
         <v>315</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>320</v>
@@ -8136,16 +8136,16 @@
         <v>46225.87127599537</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I118" s="5">
         <v>46297</v>
@@ -8166,7 +8166,7 @@
         <v>315</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>315</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46225.869796087965</v>
+        <v>46283.14666770834</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>145</v>
@@ -3806,8 +3806,8 @@
       <c r="R39" s="9">
         <v>46290</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>32</v>
+      <c r="S39" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
